--- a/artfynd/A 40837-2023 artfynd.xlsx
+++ b/artfynd/A 40837-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126306691</v>
       </c>
       <c r="B2" t="n">
-        <v>101139</v>
+        <v>101143</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40837-2023 artfynd.xlsx
+++ b/artfynd/A 40837-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126306691</v>
       </c>
       <c r="B2" t="n">
-        <v>101143</v>
+        <v>101146</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40837-2023 artfynd.xlsx
+++ b/artfynd/A 40837-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126306691</v>
       </c>
       <c r="B2" t="n">
-        <v>101146</v>
+        <v>101155</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
